--- a/supporting_material/experiments/favalli/lane-2-fasta.xlsx
+++ b/supporting_material/experiments/favalli/lane-2-fasta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/favalli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E15E4A-C6E9-B444-BCE9-8F1023C9969A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2127D5-8DB5-0045-80C5-AC79585A629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4447,9 +4447,6 @@
     <t>TGTCAC</t>
   </si>
   <si>
-    <t>lane-2</t>
-  </si>
-  <si>
     <t>CAIX_ss</t>
   </si>
   <si>
@@ -4592,6 +4589,9 @@
   </si>
   <si>
     <t>./20190812.A-1907_NF2GB2_s2_R1.fasta.gz</t>
+  </si>
+  <si>
+    <t>lane-2-fasta</t>
   </si>
 </sst>
 </file>
@@ -5253,7 +5253,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1467</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -5261,7 +5261,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -5308,10 +5308,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="42" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>1513</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -6381,7 +6381,7 @@
         <v>422</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -6395,7 +6395,7 @@
         <v>422</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -6409,7 +6409,7 @@
         <v>422</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -6423,10 +6423,10 @@
         <v>422</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E101" s="38" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -6440,10 +6440,10 @@
         <v>422</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E102" s="38" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -6457,10 +6457,10 @@
         <v>422</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -6474,7 +6474,7 @@
         <v>422</v>
       </c>
       <c r="D104" s="40" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -6488,7 +6488,7 @@
         <v>422</v>
       </c>
       <c r="D105" s="40" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -6502,7 +6502,7 @@
         <v>422</v>
       </c>
       <c r="D106" s="40" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -6516,7 +6516,7 @@
         <v>422</v>
       </c>
       <c r="D107" s="40" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -6530,7 +6530,7 @@
         <v>422</v>
       </c>
       <c r="D108" s="40" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -6544,7 +6544,7 @@
         <v>422</v>
       </c>
       <c r="D109" s="40" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -6558,7 +6558,7 @@
         <v>422</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -6572,7 +6572,7 @@
         <v>422</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -6586,7 +6586,7 @@
         <v>422</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -6600,7 +6600,7 @@
         <v>422</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -6614,7 +6614,7 @@
         <v>422</v>
       </c>
       <c r="D114" s="40" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -6628,7 +6628,7 @@
         <v>422</v>
       </c>
       <c r="D115" s="40" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -6642,7 +6642,7 @@
         <v>422</v>
       </c>
       <c r="D116" s="40" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -6656,7 +6656,7 @@
         <v>422</v>
       </c>
       <c r="D117" s="40" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -6670,7 +6670,7 @@
         <v>422</v>
       </c>
       <c r="D118" s="40" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -6684,10 +6684,10 @@
         <v>422</v>
       </c>
       <c r="D119" s="40" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E119" s="39" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -6701,10 +6701,10 @@
         <v>422</v>
       </c>
       <c r="D120" s="40" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E120" s="39" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -6718,10 +6718,10 @@
         <v>422</v>
       </c>
       <c r="D121" s="40" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E121" s="39" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -6735,7 +6735,7 @@
         <v>422</v>
       </c>
       <c r="D122" s="40" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -6749,7 +6749,7 @@
         <v>422</v>
       </c>
       <c r="D123" s="40" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -6763,7 +6763,7 @@
         <v>422</v>
       </c>
       <c r="D124" s="40" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -6777,7 +6777,7 @@
         <v>422</v>
       </c>
       <c r="D125" s="40" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -6791,7 +6791,7 @@
         <v>422</v>
       </c>
       <c r="D126" s="40" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -6805,7 +6805,7 @@
         <v>422</v>
       </c>
       <c r="D127" s="40" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -6819,7 +6819,7 @@
         <v>422</v>
       </c>
       <c r="D128" s="40" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -6833,7 +6833,7 @@
         <v>422</v>
       </c>
       <c r="D129" s="40" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -6847,7 +6847,7 @@
         <v>422</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -6861,7 +6861,7 @@
         <v>422</v>
       </c>
       <c r="D131" s="40" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -6875,7 +6875,7 @@
         <v>422</v>
       </c>
       <c r="D132" s="40" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -6889,7 +6889,7 @@
         <v>422</v>
       </c>
       <c r="D133" s="40" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
@@ -6903,7 +6903,7 @@
         <v>422</v>
       </c>
       <c r="D134" s="40" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -6917,7 +6917,7 @@
         <v>422</v>
       </c>
       <c r="D135" s="40" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -6931,7 +6931,7 @@
         <v>422</v>
       </c>
       <c r="D136" s="40" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -6945,7 +6945,7 @@
         <v>422</v>
       </c>
       <c r="D137" s="40" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -6959,7 +6959,7 @@
         <v>422</v>
       </c>
       <c r="D138" s="40" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -6973,7 +6973,7 @@
         <v>422</v>
       </c>
       <c r="D139" s="40" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -6987,7 +6987,7 @@
         <v>422</v>
       </c>
       <c r="D140" s="40" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
@@ -7001,7 +7001,7 @@
         <v>422</v>
       </c>
       <c r="D141" s="40" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
@@ -7015,7 +7015,7 @@
         <v>422</v>
       </c>
       <c r="D142" s="40" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
@@ -7029,7 +7029,7 @@
         <v>422</v>
       </c>
       <c r="D143" s="40" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
@@ -7043,7 +7043,7 @@
         <v>422</v>
       </c>
       <c r="D144" s="40" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
@@ -7057,7 +7057,7 @@
         <v>422</v>
       </c>
       <c r="D145" s="40" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
@@ -7071,7 +7071,7 @@
         <v>422</v>
       </c>
       <c r="D146" s="40" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
@@ -7085,7 +7085,7 @@
         <v>422</v>
       </c>
       <c r="D147" s="40" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
@@ -7099,7 +7099,7 @@
         <v>422</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
@@ -7113,7 +7113,7 @@
         <v>422</v>
       </c>
       <c r="D149" s="40" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
@@ -7127,7 +7127,7 @@
         <v>422</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
@@ -7141,7 +7141,7 @@
         <v>422</v>
       </c>
       <c r="D151" s="40" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
@@ -7155,7 +7155,7 @@
         <v>422</v>
       </c>
       <c r="D152" s="40" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
@@ -7169,7 +7169,7 @@
         <v>422</v>
       </c>
       <c r="D153" s="40" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
@@ -7183,7 +7183,7 @@
         <v>422</v>
       </c>
       <c r="D154" s="40" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
@@ -7197,7 +7197,7 @@
         <v>422</v>
       </c>
       <c r="D155" s="40" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
@@ -7211,7 +7211,7 @@
         <v>422</v>
       </c>
       <c r="D156" s="40" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
@@ -7225,7 +7225,7 @@
         <v>422</v>
       </c>
       <c r="D157" s="40" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
@@ -7239,7 +7239,7 @@
         <v>422</v>
       </c>
       <c r="D158" s="40" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
@@ -7253,7 +7253,7 @@
         <v>422</v>
       </c>
       <c r="D159" s="40" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
@@ -7267,7 +7267,7 @@
         <v>422</v>
       </c>
       <c r="D160" s="40" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
@@ -7281,7 +7281,7 @@
         <v>422</v>
       </c>
       <c r="D161" s="40" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
@@ -7295,7 +7295,7 @@
         <v>422</v>
       </c>
       <c r="D162" s="40" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
@@ -7309,7 +7309,7 @@
         <v>422</v>
       </c>
       <c r="D163" s="40" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
@@ -7323,7 +7323,7 @@
         <v>422</v>
       </c>
       <c r="D164" s="40" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
@@ -7337,7 +7337,7 @@
         <v>422</v>
       </c>
       <c r="D165" s="40" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
@@ -7351,7 +7351,7 @@
         <v>422</v>
       </c>
       <c r="D166" s="40" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
@@ -7365,7 +7365,7 @@
         <v>422</v>
       </c>
       <c r="D167" s="40" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
@@ -7379,7 +7379,7 @@
         <v>422</v>
       </c>
       <c r="D168" s="40" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
@@ -7393,7 +7393,7 @@
         <v>422</v>
       </c>
       <c r="D169" s="40" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
@@ -7407,7 +7407,7 @@
         <v>422</v>
       </c>
       <c r="D170" s="40" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
@@ -7421,7 +7421,7 @@
         <v>422</v>
       </c>
       <c r="D171" s="40" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
@@ -7435,7 +7435,7 @@
         <v>422</v>
       </c>
       <c r="D172" s="40" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
@@ -7449,7 +7449,7 @@
         <v>422</v>
       </c>
       <c r="D173" s="40" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
@@ -7463,7 +7463,7 @@
         <v>422</v>
       </c>
       <c r="D174" s="40" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
@@ -7477,7 +7477,7 @@
         <v>422</v>
       </c>
       <c r="D175" s="40" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
@@ -7491,7 +7491,7 @@
         <v>422</v>
       </c>
       <c r="D176" s="40" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
@@ -7505,7 +7505,7 @@
         <v>422</v>
       </c>
       <c r="D177" s="40" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
@@ -7519,7 +7519,7 @@
         <v>422</v>
       </c>
       <c r="D178" s="40" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
@@ -7533,7 +7533,7 @@
         <v>422</v>
       </c>
       <c r="D179" s="40" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
@@ -7547,7 +7547,7 @@
         <v>422</v>
       </c>
       <c r="D180" s="40" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
@@ -7561,7 +7561,7 @@
         <v>422</v>
       </c>
       <c r="D181" s="40" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
@@ -7575,7 +7575,7 @@
         <v>422</v>
       </c>
       <c r="D182" s="40" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
@@ -7589,7 +7589,7 @@
         <v>422</v>
       </c>
       <c r="D183" s="40" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
@@ -7603,7 +7603,7 @@
         <v>422</v>
       </c>
       <c r="D184" s="40" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
@@ -7617,7 +7617,7 @@
         <v>422</v>
       </c>
       <c r="D185" s="40" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
@@ -7631,7 +7631,7 @@
         <v>422</v>
       </c>
       <c r="D186" s="40" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
@@ -7645,7 +7645,7 @@
         <v>422</v>
       </c>
       <c r="D187" s="40" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
@@ -7659,7 +7659,7 @@
         <v>422</v>
       </c>
       <c r="D188" s="40" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
@@ -7673,7 +7673,7 @@
         <v>422</v>
       </c>
       <c r="D189" s="40" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
@@ -7687,7 +7687,7 @@
         <v>422</v>
       </c>
       <c r="D190" s="40" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
@@ -7701,7 +7701,7 @@
         <v>422</v>
       </c>
       <c r="D191" s="40" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
@@ -7715,7 +7715,7 @@
         <v>422</v>
       </c>
       <c r="D192" s="40" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
@@ -7729,7 +7729,7 @@
         <v>422</v>
       </c>
       <c r="D193" s="40" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
